--- a/data/ocean-freight.xlsx
+++ b/data/ocean-freight.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maru\Desktop\AI\케이브릿지 웹페이지\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jin\Desktop\AI\웹페이지\02060808\KBDGFW-main-optimized\KBDGFW-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EBDF8A1-232D-4706-BE01-479B72B1105E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BE1830-CD18-469B-B479-0C1809C835B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25510" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -1201,7 +1201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -1241,7 +1241,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="28">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="27.6">
+    <row r="7" spans="1:2" ht="28">
       <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27.6">
+    <row r="9" spans="1:2" ht="28">
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="27.6">
+    <row r="10" spans="1:2" ht="28">
       <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
@@ -1361,7 +1361,7 @@
       <c r="A21" s="7"/>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:2" ht="27.6">
+    <row r="22" spans="1:2" ht="28">
       <c r="A22" s="9" t="s">
         <v>35</v>
       </c>
@@ -1381,7 +1381,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H500"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1392,7 +1392,7 @@
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.2" customHeight="1">
+    <row r="1" spans="1:8" ht="19.25" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.05" customHeight="1">
+    <row r="2" spans="1:8" ht="16" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>37</v>
       </c>
@@ -1432,17 +1432,17 @@
         <v>40</v>
       </c>
       <c r="E2" s="13">
-        <v>8000</v>
+        <v>9050</v>
       </c>
       <c r="F2" s="13">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="G2" s="16">
         <v>1</v>
       </c>
       <c r="H2" s="11"/>
     </row>
-    <row r="3" spans="1:8" ht="16.05" customHeight="1">
+    <row r="3" spans="1:8" ht="16" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
@@ -1456,17 +1456,17 @@
         <v>42</v>
       </c>
       <c r="E3" s="13">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="F3" s="13">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="G3" s="16">
         <v>2</v>
       </c>
       <c r="H3" s="11"/>
     </row>
-    <row r="4" spans="1:8" ht="16.05" customHeight="1">
+    <row r="4" spans="1:8" ht="16" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>37</v>
       </c>
@@ -1480,17 +1480,17 @@
         <v>44</v>
       </c>
       <c r="E4" s="13">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="F4" s="13">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="G4" s="16">
         <v>3</v>
       </c>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:8" ht="16.05" customHeight="1">
+    <row r="5" spans="1:8" ht="16" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>37</v>
       </c>
@@ -1504,17 +1504,17 @@
         <v>46</v>
       </c>
       <c r="E5" s="13">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="F5" s="13">
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="G5" s="16">
         <v>4</v>
       </c>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:8" ht="16.05" customHeight="1">
+    <row r="6" spans="1:8" ht="16" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>37</v>
       </c>
@@ -1528,17 +1528,17 @@
         <v>48</v>
       </c>
       <c r="E6" s="13">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="F6" s="13">
-        <v>7550</v>
+        <v>7600</v>
       </c>
       <c r="G6" s="16">
         <v>5</v>
       </c>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:8" ht="16.05" customHeight="1">
+    <row r="7" spans="1:8" ht="16" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>37</v>
       </c>
@@ -1552,17 +1552,17 @@
         <v>50</v>
       </c>
       <c r="E7" s="13">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="F7" s="13">
-        <v>7550</v>
+        <v>7600</v>
       </c>
       <c r="G7" s="16">
         <v>6</v>
       </c>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:8" ht="16.05" customHeight="1">
+    <row r="8" spans="1:8" ht="16" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -1576,17 +1576,17 @@
         <v>52</v>
       </c>
       <c r="E8" s="13">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="F8" s="13">
-        <v>7550</v>
+        <v>7600</v>
       </c>
       <c r="G8" s="16">
         <v>7</v>
       </c>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:8" ht="16.05" customHeight="1">
+    <row r="9" spans="1:8" ht="16" customHeight="1">
       <c r="A9" s="11" t="s">
         <v>37</v>
       </c>
@@ -1600,17 +1600,17 @@
         <v>54</v>
       </c>
       <c r="E9" s="13">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="F9" s="13">
-        <v>7550</v>
+        <v>7600</v>
       </c>
       <c r="G9" s="16">
         <v>8</v>
       </c>
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:8" ht="16.05" customHeight="1">
+    <row r="10" spans="1:8" ht="16" customHeight="1">
       <c r="A10" s="11" t="s">
         <v>37</v>
       </c>
@@ -1624,17 +1624,17 @@
         <v>56</v>
       </c>
       <c r="E10" s="13">
-        <v>8600</v>
+        <v>9050</v>
       </c>
       <c r="F10" s="13">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="G10" s="16">
         <v>9</v>
       </c>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:8" ht="16.05" customHeight="1">
+    <row r="11" spans="1:8" ht="16" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>37</v>
       </c>
@@ -1648,17 +1648,17 @@
         <v>58</v>
       </c>
       <c r="E11" s="13">
-        <v>8600</v>
+        <v>9050</v>
       </c>
       <c r="F11" s="13">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="G11" s="16">
         <v>10</v>
       </c>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:8" ht="16.05" customHeight="1">
+    <row r="12" spans="1:8" ht="16" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>37</v>
       </c>
@@ -1672,17 +1672,17 @@
         <v>60</v>
       </c>
       <c r="E12" s="13">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="F12" s="13">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="G12" s="16">
         <v>11</v>
       </c>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:8" ht="16.05" customHeight="1">
+    <row r="13" spans="1:8" ht="16" customHeight="1">
       <c r="A13" s="11" t="s">
         <v>37</v>
       </c>
@@ -1696,17 +1696,17 @@
         <v>62</v>
       </c>
       <c r="E13" s="13">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="F13" s="13">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="G13" s="16">
         <v>12</v>
       </c>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:8" ht="16.05" customHeight="1">
+    <row r="14" spans="1:8" ht="16" customHeight="1">
       <c r="A14" s="11" t="s">
         <v>37</v>
       </c>
@@ -1720,17 +1720,17 @@
         <v>64</v>
       </c>
       <c r="E14" s="13">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="F14" s="13">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="G14" s="16">
         <v>13</v>
       </c>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:8" ht="16.05" customHeight="1">
+    <row r="15" spans="1:8" ht="16" customHeight="1">
       <c r="A15" s="11" t="s">
         <v>37</v>
       </c>
@@ -1744,17 +1744,17 @@
         <v>67</v>
       </c>
       <c r="E15" s="13">
-        <v>5350</v>
+        <v>5500</v>
       </c>
       <c r="F15" s="13">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="G15" s="16">
         <v>1</v>
       </c>
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:8" ht="16.05" customHeight="1">
+    <row r="16" spans="1:8" ht="16" customHeight="1">
       <c r="A16" s="11" t="s">
         <v>37</v>
       </c>
@@ -1768,17 +1768,17 @@
         <v>69</v>
       </c>
       <c r="E16" s="13">
-        <v>7200</v>
+        <v>6800</v>
       </c>
       <c r="F16" s="13">
-        <v>7400</v>
+        <v>7000</v>
       </c>
       <c r="G16" s="16">
         <v>2</v>
       </c>
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="1:8" ht="16.05" customHeight="1">
+    <row r="17" spans="1:8" ht="16" customHeight="1">
       <c r="A17" s="11" t="s">
         <v>37</v>
       </c>
@@ -1792,17 +1792,17 @@
         <v>71</v>
       </c>
       <c r="E17" s="13">
-        <v>7200</v>
+        <v>6800</v>
       </c>
       <c r="F17" s="13">
-        <v>7400</v>
+        <v>7000</v>
       </c>
       <c r="G17" s="16">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="1:8" ht="16.05" customHeight="1">
+    <row r="18" spans="1:8" ht="16" customHeight="1">
       <c r="A18" s="11" t="s">
         <v>37</v>
       </c>
@@ -1816,17 +1816,17 @@
         <v>73</v>
       </c>
       <c r="E18" s="13">
-        <v>7200</v>
+        <v>6800</v>
       </c>
       <c r="F18" s="13">
-        <v>7400</v>
+        <v>7000</v>
       </c>
       <c r="G18" s="16">
         <v>4</v>
       </c>
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="1:8" ht="16.05" customHeight="1">
+    <row r="19" spans="1:8" ht="16" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>37</v>
       </c>
@@ -1840,17 +1840,17 @@
         <v>75</v>
       </c>
       <c r="E19" s="13">
-        <v>5550</v>
+        <v>5500</v>
       </c>
       <c r="F19" s="13">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="G19" s="16">
         <v>5</v>
       </c>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" spans="1:8" ht="16.05" customHeight="1">
+    <row r="20" spans="1:8" ht="16" customHeight="1">
       <c r="A20" s="11" t="s">
         <v>37</v>
       </c>
@@ -1864,17 +1864,17 @@
         <v>77</v>
       </c>
       <c r="E20" s="13">
-        <v>5550</v>
+        <v>5500</v>
       </c>
       <c r="F20" s="13">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="G20" s="16">
         <v>6</v>
       </c>
       <c r="H20" s="11"/>
     </row>
-    <row r="21" spans="1:8" ht="16.05" customHeight="1">
+    <row r="21" spans="1:8" ht="16" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>37</v>
       </c>
@@ -1888,17 +1888,17 @@
         <v>79</v>
       </c>
       <c r="E21" s="13">
-        <v>6350</v>
+        <v>7500</v>
       </c>
       <c r="F21" s="13">
-        <v>6700</v>
+        <v>7700</v>
       </c>
       <c r="G21" s="16">
         <v>7</v>
       </c>
       <c r="H21" s="11"/>
     </row>
-    <row r="22" spans="1:8" ht="16.05" customHeight="1">
+    <row r="22" spans="1:8" ht="16" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>37</v>
       </c>
@@ -1912,17 +1912,17 @@
         <v>81</v>
       </c>
       <c r="E22" s="13">
-        <v>6350</v>
+        <v>7500</v>
       </c>
       <c r="F22" s="13">
-        <v>6700</v>
+        <v>7700</v>
       </c>
       <c r="G22" s="16">
         <v>8</v>
       </c>
       <c r="H22" s="11"/>
     </row>
-    <row r="23" spans="1:8" ht="16.05" customHeight="1">
+    <row r="23" spans="1:8" ht="16" customHeight="1">
       <c r="A23" s="11" t="s">
         <v>37</v>
       </c>
@@ -1936,17 +1936,17 @@
         <v>84</v>
       </c>
       <c r="E23" s="13">
-        <v>4600</v>
+        <v>4050</v>
       </c>
       <c r="F23" s="13">
-        <v>6800</v>
+        <v>6350</v>
       </c>
       <c r="G23" s="16">
         <v>1</v>
       </c>
       <c r="H23" s="11"/>
     </row>
-    <row r="24" spans="1:8" ht="16.05" customHeight="1">
+    <row r="24" spans="1:8" ht="16" customHeight="1">
       <c r="A24" s="11" t="s">
         <v>37</v>
       </c>
@@ -1960,17 +1960,17 @@
         <v>86</v>
       </c>
       <c r="E24" s="13">
-        <v>4600</v>
+        <v>4050</v>
       </c>
       <c r="F24" s="13">
-        <v>6800</v>
+        <v>6350</v>
       </c>
       <c r="G24" s="16">
         <v>2</v>
       </c>
       <c r="H24" s="11"/>
     </row>
-    <row r="25" spans="1:8" ht="16.05" customHeight="1">
+    <row r="25" spans="1:8" ht="16" customHeight="1">
       <c r="A25" s="11" t="s">
         <v>37</v>
       </c>
@@ -1984,17 +1984,17 @@
         <v>88</v>
       </c>
       <c r="E25" s="13">
-        <v>4600</v>
+        <v>4050</v>
       </c>
       <c r="F25" s="13">
-        <v>6800</v>
+        <v>6350</v>
       </c>
       <c r="G25" s="16">
         <v>3</v>
       </c>
       <c r="H25" s="11"/>
     </row>
-    <row r="26" spans="1:8" ht="16.05" customHeight="1">
+    <row r="26" spans="1:8" ht="16" customHeight="1">
       <c r="A26" s="11" t="s">
         <v>37</v>
       </c>
@@ -2008,17 +2008,17 @@
         <v>90</v>
       </c>
       <c r="E26" s="13">
-        <v>3700</v>
+        <v>3380</v>
       </c>
       <c r="F26" s="13">
-        <v>5800</v>
+        <v>5350</v>
       </c>
       <c r="G26" s="16">
         <v>4</v>
       </c>
       <c r="H26" s="11"/>
     </row>
-    <row r="27" spans="1:8" ht="16.05" customHeight="1">
+    <row r="27" spans="1:8" ht="16" customHeight="1">
       <c r="A27" s="11" t="s">
         <v>37</v>
       </c>
@@ -2032,17 +2032,17 @@
         <v>92</v>
       </c>
       <c r="E27" s="13">
-        <v>3700</v>
+        <v>3380</v>
       </c>
       <c r="F27" s="13">
-        <v>5800</v>
+        <v>5350</v>
       </c>
       <c r="G27" s="16">
         <v>5</v>
       </c>
       <c r="H27" s="11"/>
     </row>
-    <row r="28" spans="1:8" ht="16.05" customHeight="1">
+    <row r="28" spans="1:8" ht="16" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>37</v>
       </c>
@@ -2056,17 +2056,17 @@
         <v>94</v>
       </c>
       <c r="E28" s="13">
-        <v>3700</v>
+        <v>3380</v>
       </c>
       <c r="F28" s="13">
-        <v>5800</v>
+        <v>5350</v>
       </c>
       <c r="G28" s="16">
         <v>6</v>
       </c>
       <c r="H28" s="11"/>
     </row>
-    <row r="29" spans="1:8" ht="16.05" customHeight="1">
+    <row r="29" spans="1:8" ht="16" customHeight="1">
       <c r="A29" s="11" t="s">
         <v>37</v>
       </c>
@@ -2080,17 +2080,17 @@
         <v>96</v>
       </c>
       <c r="E29" s="13">
-        <v>3700</v>
+        <v>3380</v>
       </c>
       <c r="F29" s="13">
-        <v>5800</v>
+        <v>5350</v>
       </c>
       <c r="G29" s="16">
         <v>7</v>
       </c>
       <c r="H29" s="11"/>
     </row>
-    <row r="30" spans="1:8" ht="16.05" customHeight="1">
+    <row r="30" spans="1:8" ht="16" customHeight="1">
       <c r="A30" s="11" t="s">
         <v>37</v>
       </c>
@@ -2104,17 +2104,17 @@
         <v>98</v>
       </c>
       <c r="E30" s="13">
-        <v>3700</v>
+        <v>3380</v>
       </c>
       <c r="F30" s="13">
-        <v>5800</v>
+        <v>5350</v>
       </c>
       <c r="G30" s="16">
         <v>8</v>
       </c>
       <c r="H30" s="11"/>
     </row>
-    <row r="31" spans="1:8" ht="16.05" customHeight="1">
+    <row r="31" spans="1:8" ht="16" customHeight="1">
       <c r="A31" s="11" t="s">
         <v>37</v>
       </c>
@@ -2128,17 +2128,17 @@
         <v>100</v>
       </c>
       <c r="E31" s="13">
-        <v>4600</v>
+        <v>4200</v>
       </c>
       <c r="F31" s="13">
-        <v>6800</v>
+        <v>6550</v>
       </c>
       <c r="G31" s="16">
         <v>9</v>
       </c>
       <c r="H31" s="11"/>
     </row>
-    <row r="32" spans="1:8" ht="16.05" customHeight="1">
+    <row r="32" spans="1:8" ht="16" customHeight="1">
       <c r="A32" s="11" t="s">
         <v>37</v>
       </c>
@@ -2152,17 +2152,17 @@
         <v>102</v>
       </c>
       <c r="E32" s="13">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="F32" s="13">
-        <v>6400</v>
+        <v>5350</v>
       </c>
       <c r="G32" s="16">
         <v>10</v>
       </c>
       <c r="H32" s="11"/>
     </row>
-    <row r="33" spans="1:8" ht="16.05" customHeight="1">
+    <row r="33" spans="1:8" ht="16" customHeight="1">
       <c r="A33" s="11" t="s">
         <v>37</v>
       </c>
@@ -2179,14 +2179,14 @@
         <v>4200</v>
       </c>
       <c r="F33" s="13">
-        <v>6800</v>
+        <v>6550</v>
       </c>
       <c r="G33" s="16">
         <v>11</v>
       </c>
       <c r="H33" s="11"/>
     </row>
-    <row r="34" spans="1:8" ht="16.05" customHeight="1">
+    <row r="34" spans="1:8" ht="16" customHeight="1">
       <c r="A34" s="11" t="s">
         <v>37</v>
       </c>
@@ -2203,14 +2203,14 @@
         <v>4200</v>
       </c>
       <c r="F34" s="13">
-        <v>6800</v>
+        <v>6550</v>
       </c>
       <c r="G34" s="16">
         <v>12</v>
       </c>
       <c r="H34" s="11"/>
     </row>
-    <row r="35" spans="1:8" ht="16.05" customHeight="1">
+    <row r="35" spans="1:8" ht="16" customHeight="1">
       <c r="A35" s="11" t="s">
         <v>37</v>
       </c>
@@ -2224,17 +2224,17 @@
         <v>108</v>
       </c>
       <c r="E35" s="13">
-        <v>4200</v>
+        <v>4250</v>
       </c>
       <c r="F35" s="13">
-        <v>6800</v>
+        <v>6650</v>
       </c>
       <c r="G35" s="16">
         <v>13</v>
       </c>
       <c r="H35" s="11"/>
     </row>
-    <row r="36" spans="1:8" ht="16.05" customHeight="1">
+    <row r="36" spans="1:8" ht="16" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>37</v>
       </c>
@@ -2248,17 +2248,17 @@
         <v>110</v>
       </c>
       <c r="E36" s="13">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="F36" s="13">
-        <v>6400</v>
+        <v>5450</v>
       </c>
       <c r="G36" s="16">
         <v>14</v>
       </c>
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:8" ht="16.05" customHeight="1">
+    <row r="37" spans="1:8" ht="16" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>37</v>
       </c>
@@ -2272,17 +2272,17 @@
         <v>113</v>
       </c>
       <c r="E37" s="13">
-        <v>3050</v>
+        <v>1750</v>
       </c>
       <c r="F37" s="13">
-        <v>4900</v>
+        <v>1900</v>
       </c>
       <c r="G37" s="16">
         <v>1</v>
       </c>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" ht="16.05" customHeight="1">
+    <row r="38" spans="1:8" ht="16" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>37</v>
       </c>
@@ -2296,17 +2296,17 @@
         <v>115</v>
       </c>
       <c r="E38" s="13">
-        <v>1950</v>
+        <v>1450</v>
       </c>
       <c r="F38" s="13">
-        <v>2550</v>
+        <v>1800</v>
       </c>
       <c r="G38" s="16">
         <v>2</v>
       </c>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" ht="16.05" customHeight="1">
+    <row r="39" spans="1:8" ht="16" customHeight="1">
       <c r="A39" s="11" t="s">
         <v>37</v>
       </c>
@@ -2320,17 +2320,17 @@
         <v>117</v>
       </c>
       <c r="E39" s="13">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="F39" s="13">
-        <v>2500</v>
+        <v>2650</v>
       </c>
       <c r="G39" s="16">
         <v>3</v>
       </c>
       <c r="H39" s="11"/>
     </row>
-    <row r="40" spans="1:8" ht="16.05" customHeight="1">
+    <row r="40" spans="1:8" ht="16" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>37</v>
       </c>
@@ -2344,17 +2344,17 @@
         <v>119</v>
       </c>
       <c r="E40" s="13">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="F40" s="13">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G40" s="16">
         <v>4</v>
       </c>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" ht="16.05" customHeight="1">
+    <row r="41" spans="1:8" ht="16" customHeight="1">
       <c r="A41" s="11" t="s">
         <v>37</v>
       </c>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" ht="16.05" customHeight="1">
+    <row r="42" spans="1:8" ht="16" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>37</v>
       </c>
@@ -2392,17 +2392,17 @@
         <v>123</v>
       </c>
       <c r="E42" s="13">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F42" s="13">
-        <v>1300</v>
+        <v>1150</v>
       </c>
       <c r="G42" s="16">
         <v>6</v>
       </c>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" ht="16.05" customHeight="1">
+    <row r="43" spans="1:8" ht="16" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>37</v>
       </c>
@@ -2416,17 +2416,17 @@
         <v>125</v>
       </c>
       <c r="E43" s="13">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F43" s="13">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="G43" s="16">
         <v>7</v>
       </c>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" ht="16.05" customHeight="1">
+    <row r="44" spans="1:8" ht="16" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>37</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>127</v>
       </c>
       <c r="E44" s="13">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="F44" s="13">
         <v>1000</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H44" s="11"/>
     </row>
-    <row r="45" spans="1:8" ht="16.05" customHeight="1">
+    <row r="45" spans="1:8" ht="16" customHeight="1">
       <c r="A45" s="11" t="s">
         <v>37</v>
       </c>
@@ -2467,14 +2467,14 @@
         <v>650</v>
       </c>
       <c r="F45" s="13">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="G45" s="16">
         <v>9</v>
       </c>
       <c r="H45" s="11"/>
     </row>
-    <row r="46" spans="1:8" ht="16.05" customHeight="1">
+    <row r="46" spans="1:8" ht="16" customHeight="1">
       <c r="A46" s="11" t="s">
         <v>37</v>
       </c>
@@ -2491,14 +2491,14 @@
         <v>500</v>
       </c>
       <c r="F46" s="13">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="G46" s="16">
         <v>10</v>
       </c>
       <c r="H46" s="11"/>
     </row>
-    <row r="47" spans="1:8" ht="16.05" customHeight="1">
+    <row r="47" spans="1:8" ht="16" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>37</v>
       </c>
@@ -2512,17 +2512,17 @@
         <v>133</v>
       </c>
       <c r="E47" s="13">
-        <v>850</v>
+        <v>525</v>
       </c>
       <c r="F47" s="13">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G47" s="16">
         <v>11</v>
       </c>
       <c r="H47" s="11"/>
     </row>
-    <row r="48" spans="1:8" ht="16.05" customHeight="1">
+    <row r="48" spans="1:8" ht="16" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>37</v>
       </c>
@@ -2536,17 +2536,17 @@
         <v>135</v>
       </c>
       <c r="E48" s="13">
-        <v>350</v>
+        <v>225</v>
       </c>
       <c r="F48" s="13">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="G48" s="16">
         <v>12</v>
       </c>
       <c r="H48" s="11"/>
     </row>
-    <row r="49" spans="1:8" ht="16.05" customHeight="1">
+    <row r="49" spans="1:8" ht="16" customHeight="1">
       <c r="A49" s="11" t="s">
         <v>37</v>
       </c>
@@ -2560,17 +2560,17 @@
         <v>137</v>
       </c>
       <c r="E49" s="13">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="F49" s="13">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G49" s="16">
         <v>13</v>
       </c>
       <c r="H49" s="11"/>
     </row>
-    <row r="50" spans="1:8" ht="16.05" customHeight="1">
+    <row r="50" spans="1:8" ht="16" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>37</v>
       </c>
@@ -2587,14 +2587,14 @@
         <v>600</v>
       </c>
       <c r="F50" s="13">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G50" s="16">
         <v>14</v>
       </c>
       <c r="H50" s="11"/>
     </row>
-    <row r="51" spans="1:8" ht="16.05" customHeight="1">
+    <row r="51" spans="1:8" ht="16" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>37</v>
       </c>
@@ -2608,17 +2608,17 @@
         <v>141</v>
       </c>
       <c r="E51" s="13">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F51" s="13">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="G51" s="16">
         <v>15</v>
       </c>
       <c r="H51" s="11"/>
     </row>
-    <row r="52" spans="1:8" ht="16.05" customHeight="1">
+    <row r="52" spans="1:8" ht="16" customHeight="1">
       <c r="A52" s="11" t="s">
         <v>37</v>
       </c>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="H52" s="11"/>
     </row>
-    <row r="53" spans="1:8" ht="16.05" customHeight="1">
+    <row r="53" spans="1:8" ht="16" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>37</v>
       </c>
@@ -2656,17 +2656,17 @@
         <v>145</v>
       </c>
       <c r="E53" s="13">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F53" s="13">
-        <v>900</v>
+        <v>650</v>
       </c>
       <c r="G53" s="16">
         <v>17</v>
       </c>
       <c r="H53" s="11"/>
     </row>
-    <row r="54" spans="1:8" ht="16.05" customHeight="1">
+    <row r="54" spans="1:8" ht="16" customHeight="1">
       <c r="A54" s="11" t="s">
         <v>37</v>
       </c>
@@ -2680,17 +2680,17 @@
         <v>147</v>
       </c>
       <c r="E54" s="13">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F54" s="13">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="G54" s="16">
         <v>18</v>
       </c>
       <c r="H54" s="11"/>
     </row>
-    <row r="55" spans="1:8" ht="16.05" customHeight="1">
+    <row r="55" spans="1:8" ht="16" customHeight="1">
       <c r="A55" s="11" t="s">
         <v>37</v>
       </c>
@@ -2704,17 +2704,17 @@
         <v>149</v>
       </c>
       <c r="E55" s="13">
-        <v>2000</v>
+        <v>1550</v>
       </c>
       <c r="F55" s="13">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="G55" s="16">
         <v>19</v>
       </c>
       <c r="H55" s="11"/>
     </row>
-    <row r="56" spans="1:8" ht="16.05" customHeight="1">
+    <row r="56" spans="1:8" ht="16" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>37</v>
       </c>
@@ -2728,17 +2728,17 @@
         <v>151</v>
       </c>
       <c r="E56" s="13">
-        <v>1450</v>
+        <v>1175</v>
       </c>
       <c r="F56" s="13">
-        <v>2250</v>
+        <v>2150</v>
       </c>
       <c r="G56" s="16">
         <v>20</v>
       </c>
       <c r="H56" s="11"/>
     </row>
-    <row r="57" spans="1:8" ht="16.05" customHeight="1">
+    <row r="57" spans="1:8" ht="16" customHeight="1">
       <c r="A57" s="11" t="s">
         <v>37</v>
       </c>
@@ -2752,17 +2752,17 @@
         <v>153</v>
       </c>
       <c r="E57" s="13">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="F57" s="13">
-        <v>2000</v>
+        <v>1650</v>
       </c>
       <c r="G57" s="16">
         <v>21</v>
       </c>
       <c r="H57" s="11"/>
     </row>
-    <row r="58" spans="1:8" ht="16.05" customHeight="1">
+    <row r="58" spans="1:8" ht="16" customHeight="1">
       <c r="A58" s="11" t="s">
         <v>37</v>
       </c>
@@ -2776,17 +2776,17 @@
         <v>155</v>
       </c>
       <c r="E58" s="13">
-        <v>2050</v>
+        <v>1650</v>
       </c>
       <c r="F58" s="13">
-        <v>2500</v>
+        <v>1950</v>
       </c>
       <c r="G58" s="16">
         <v>22</v>
       </c>
       <c r="H58" s="11"/>
     </row>
-    <row r="59" spans="1:8" ht="16.05" customHeight="1">
+    <row r="59" spans="1:8" ht="16" customHeight="1">
       <c r="A59" s="11" t="s">
         <v>37</v>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H59" s="11"/>
     </row>
-    <row r="60" spans="1:8" ht="16.05" customHeight="1">
+    <row r="60" spans="1:8" ht="16" customHeight="1">
       <c r="A60" s="11" t="s">
         <v>37</v>
       </c>
@@ -2824,17 +2824,17 @@
         <v>160</v>
       </c>
       <c r="E60" s="13">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="F60" s="13">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="G60" s="16">
         <v>2</v>
       </c>
       <c r="H60" s="11"/>
     </row>
-    <row r="61" spans="1:8" ht="16.05" customHeight="1">
+    <row r="61" spans="1:8" ht="16" customHeight="1">
       <c r="A61" s="11" t="s">
         <v>37</v>
       </c>
@@ -2848,17 +2848,17 @@
         <v>162</v>
       </c>
       <c r="E61" s="13">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F61" s="13">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G61" s="16">
         <v>3</v>
       </c>
       <c r="H61" s="11"/>
     </row>
-    <row r="62" spans="1:8" ht="16.05" customHeight="1">
+    <row r="62" spans="1:8" ht="16" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>37</v>
       </c>
@@ -2872,17 +2872,17 @@
         <v>164</v>
       </c>
       <c r="E62" s="13">
+        <v>50</v>
+      </c>
+      <c r="F62" s="13">
         <v>100</v>
-      </c>
-      <c r="F62" s="13">
-        <v>200</v>
       </c>
       <c r="G62" s="16">
         <v>4</v>
       </c>
       <c r="H62" s="11"/>
     </row>
-    <row r="63" spans="1:8" ht="16.05" customHeight="1">
+    <row r="63" spans="1:8" ht="16" customHeight="1">
       <c r="A63" s="11" t="s">
         <v>37</v>
       </c>
@@ -2896,17 +2896,17 @@
         <v>166</v>
       </c>
       <c r="E63" s="13">
+        <v>50</v>
+      </c>
+      <c r="F63" s="13">
         <v>100</v>
-      </c>
-      <c r="F63" s="13">
-        <v>200</v>
       </c>
       <c r="G63" s="16">
         <v>5</v>
       </c>
       <c r="H63" s="11"/>
     </row>
-    <row r="64" spans="1:8" ht="16.05" customHeight="1">
+    <row r="64" spans="1:8" ht="16" customHeight="1">
       <c r="A64" s="11" t="s">
         <v>37</v>
       </c>
@@ -2920,17 +2920,17 @@
         <v>168</v>
       </c>
       <c r="E64" s="13">
+        <v>50</v>
+      </c>
+      <c r="F64" s="13">
         <v>100</v>
-      </c>
-      <c r="F64" s="13">
-        <v>200</v>
       </c>
       <c r="G64" s="16">
         <v>6</v>
       </c>
       <c r="H64" s="11"/>
     </row>
-    <row r="65" spans="1:8" ht="16.05" customHeight="1">
+    <row r="65" spans="1:8" ht="16" customHeight="1">
       <c r="A65" s="11" t="s">
         <v>37</v>
       </c>
@@ -2944,17 +2944,17 @@
         <v>170</v>
       </c>
       <c r="E65" s="13">
+        <v>50</v>
+      </c>
+      <c r="F65" s="13">
         <v>100</v>
-      </c>
-      <c r="F65" s="13">
-        <v>200</v>
       </c>
       <c r="G65" s="16">
         <v>7</v>
       </c>
       <c r="H65" s="11"/>
     </row>
-    <row r="66" spans="1:8" ht="16.05" customHeight="1">
+    <row r="66" spans="1:8" ht="16" customHeight="1">
       <c r="A66" s="11" t="s">
         <v>37</v>
       </c>
@@ -2968,17 +2968,17 @@
         <v>172</v>
       </c>
       <c r="E66" s="13">
+        <v>50</v>
+      </c>
+      <c r="F66" s="13">
         <v>100</v>
-      </c>
-      <c r="F66" s="13">
-        <v>200</v>
       </c>
       <c r="G66" s="16">
         <v>8</v>
       </c>
       <c r="H66" s="11"/>
     </row>
-    <row r="67" spans="1:8" ht="16.05" customHeight="1">
+    <row r="67" spans="1:8" ht="16" customHeight="1">
       <c r="A67" s="11" t="s">
         <v>37</v>
       </c>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="H67" s="11"/>
     </row>
-    <row r="68" spans="1:8" ht="16.05" customHeight="1">
+    <row r="68" spans="1:8" ht="16" customHeight="1">
       <c r="A68" s="11" t="s">
         <v>37</v>
       </c>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="H68" s="11"/>
     </row>
-    <row r="69" spans="1:8" ht="16.05" customHeight="1">
+    <row r="69" spans="1:8" ht="16" customHeight="1">
       <c r="A69" s="11" t="s">
         <v>37</v>
       </c>
@@ -3040,17 +3040,17 @@
         <v>179</v>
       </c>
       <c r="E69" s="13">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F69" s="13">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G69" s="16">
         <v>3</v>
       </c>
       <c r="H69" s="11"/>
     </row>
-    <row r="70" spans="1:8" ht="16.05" customHeight="1">
+    <row r="70" spans="1:8" ht="16" customHeight="1">
       <c r="A70" s="11" t="s">
         <v>37</v>
       </c>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H70" s="11"/>
     </row>
-    <row r="71" spans="1:8" ht="16.05" customHeight="1">
+    <row r="71" spans="1:8" ht="16" customHeight="1">
       <c r="A71" s="11" t="s">
         <v>37</v>
       </c>
@@ -3088,17 +3088,17 @@
         <v>183</v>
       </c>
       <c r="E71" s="13">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="F71" s="13">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="G71" s="16">
         <v>5</v>
       </c>
       <c r="H71" s="11"/>
     </row>
-    <row r="72" spans="1:8" ht="16.05" customHeight="1">
+    <row r="72" spans="1:8" ht="16" customHeight="1">
       <c r="A72" s="11" t="s">
         <v>37</v>
       </c>
@@ -3112,17 +3112,17 @@
         <v>185</v>
       </c>
       <c r="E72" s="13">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="F72" s="13">
-        <v>650</v>
+        <v>300</v>
       </c>
       <c r="G72" s="16">
         <v>6</v>
       </c>
       <c r="H72" s="11"/>
     </row>
-    <row r="73" spans="1:8" ht="16.05" customHeight="1">
+    <row r="73" spans="1:8" ht="16" customHeight="1">
       <c r="A73" s="11" t="s">
         <v>37</v>
       </c>
@@ -3139,14 +3139,14 @@
         <v>300</v>
       </c>
       <c r="F73" s="13">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="G73" s="16">
         <v>7</v>
       </c>
       <c r="H73" s="11"/>
     </row>
-    <row r="74" spans="1:8" ht="16.05" customHeight="1">
+    <row r="74" spans="1:8" ht="16" customHeight="1">
       <c r="A74" s="11" t="s">
         <v>37</v>
       </c>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="H74" s="11"/>
     </row>
-    <row r="75" spans="1:8" ht="16.05" customHeight="1">
+    <row r="75" spans="1:8" ht="16" customHeight="1">
       <c r="A75" s="11" t="s">
         <v>37</v>
       </c>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H75" s="11"/>
     </row>
-    <row r="76" spans="1:8" ht="16.05" customHeight="1">
+    <row r="76" spans="1:8" ht="16" customHeight="1">
       <c r="A76" s="11" t="s">
         <v>37</v>
       </c>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="H76" s="11"/>
     </row>
-    <row r="77" spans="1:8" ht="16.05" customHeight="1">
+    <row r="77" spans="1:8" ht="16" customHeight="1">
       <c r="A77" s="11" t="s">
         <v>37</v>
       </c>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="H77" s="11"/>
     </row>
-    <row r="78" spans="1:8" ht="16.05" customHeight="1">
+    <row r="78" spans="1:8" ht="16" customHeight="1">
       <c r="A78" s="11" t="s">
         <v>37</v>
       </c>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H78" s="11"/>
     </row>
-    <row r="79" spans="1:8" ht="16.05" customHeight="1">
+    <row r="79" spans="1:8" ht="16" customHeight="1">
       <c r="A79" s="11" t="s">
         <v>37</v>
       </c>
@@ -3280,17 +3280,17 @@
         <v>199</v>
       </c>
       <c r="E79" s="13">
+        <v>100</v>
+      </c>
+      <c r="F79" s="13">
         <v>150</v>
-      </c>
-      <c r="F79" s="13">
-        <v>250</v>
       </c>
       <c r="G79" s="16">
         <v>13</v>
       </c>
       <c r="H79" s="11"/>
     </row>
-    <row r="80" spans="1:8" ht="16.05" customHeight="1">
+    <row r="80" spans="1:8" ht="16" customHeight="1">
       <c r="A80" s="11" t="s">
         <v>37</v>
       </c>
@@ -3304,17 +3304,17 @@
         <v>202</v>
       </c>
       <c r="E80" s="13">
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="F80" s="13">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G80" s="16">
         <v>1</v>
       </c>
       <c r="H80" s="11"/>
     </row>
-    <row r="81" spans="1:8" ht="16.05" customHeight="1">
+    <row r="81" spans="1:8" ht="16" customHeight="1">
       <c r="A81" s="11" t="s">
         <v>37</v>
       </c>
@@ -3328,17 +3328,17 @@
         <v>204</v>
       </c>
       <c r="E81" s="13">
-        <v>4200</v>
+        <v>3700</v>
       </c>
       <c r="F81" s="13">
-        <v>5650</v>
+        <v>5400</v>
       </c>
       <c r="G81" s="16">
         <v>2</v>
       </c>
       <c r="H81" s="11"/>
     </row>
-    <row r="82" spans="1:8" ht="16.05" customHeight="1">
+    <row r="82" spans="1:8" ht="16" customHeight="1">
       <c r="A82" s="11" t="s">
         <v>37</v>
       </c>
@@ -3352,17 +3352,17 @@
         <v>206</v>
       </c>
       <c r="E82" s="13">
-        <v>3900</v>
+        <v>3750</v>
       </c>
       <c r="F82" s="13">
-        <v>5300</v>
+        <v>5700</v>
       </c>
       <c r="G82" s="16">
         <v>3</v>
       </c>
       <c r="H82" s="11"/>
     </row>
-    <row r="83" spans="1:8" ht="16.05" customHeight="1">
+    <row r="83" spans="1:8" ht="16" customHeight="1">
       <c r="A83" s="11" t="s">
         <v>37</v>
       </c>
@@ -3376,17 +3376,17 @@
         <v>208</v>
       </c>
       <c r="E83" s="13">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="F83" s="13">
-        <v>5100</v>
+        <v>5150</v>
       </c>
       <c r="G83" s="16">
         <v>4</v>
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="1:8" ht="16.05" customHeight="1">
+    <row r="84" spans="1:8" ht="16" customHeight="1">
       <c r="A84" s="11" t="s">
         <v>37</v>
       </c>
@@ -3400,17 +3400,17 @@
         <v>210</v>
       </c>
       <c r="E84" s="13">
-        <v>4300</v>
+        <v>5100</v>
       </c>
       <c r="F84" s="13">
-        <v>6300</v>
+        <v>6950</v>
       </c>
       <c r="G84" s="16">
         <v>5</v>
       </c>
       <c r="H84" s="11"/>
     </row>
-    <row r="85" spans="1:8" ht="16.05" customHeight="1">
+    <row r="85" spans="1:8" ht="16" customHeight="1">
       <c r="A85" s="11" t="s">
         <v>37</v>
       </c>
@@ -3424,17 +3424,17 @@
         <v>212</v>
       </c>
       <c r="E85" s="13">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="F85" s="13">
-        <v>5100</v>
+        <v>5600</v>
       </c>
       <c r="G85" s="16">
         <v>6</v>
       </c>
       <c r="H85" s="11"/>
     </row>
-    <row r="86" spans="1:8" ht="16.05" customHeight="1">
+    <row r="86" spans="1:8" ht="16" customHeight="1">
       <c r="A86" s="11" t="s">
         <v>37</v>
       </c>
@@ -3448,17 +3448,17 @@
         <v>214</v>
       </c>
       <c r="E86" s="13">
-        <v>7000</v>
+        <v>4950</v>
       </c>
       <c r="F86" s="13">
-        <v>7700</v>
+        <v>6150</v>
       </c>
       <c r="G86" s="16">
         <v>7</v>
       </c>
       <c r="H86" s="11"/>
     </row>
-    <row r="87" spans="1:8" ht="16.05" customHeight="1">
+    <row r="87" spans="1:8" ht="16" customHeight="1">
       <c r="A87" s="11" t="s">
         <v>37</v>
       </c>
@@ -3472,17 +3472,17 @@
         <v>216</v>
       </c>
       <c r="E87" s="13">
-        <v>8000</v>
+        <v>6700</v>
       </c>
       <c r="F87" s="13">
-        <v>8800</v>
+        <v>8500</v>
       </c>
       <c r="G87" s="16">
         <v>8</v>
       </c>
       <c r="H87" s="11"/>
     </row>
-    <row r="88" spans="1:8" ht="16.05" customHeight="1">
+    <row r="88" spans="1:8" ht="16" customHeight="1">
       <c r="A88" s="11" t="s">
         <v>37</v>
       </c>
@@ -3496,17 +3496,17 @@
         <v>218</v>
       </c>
       <c r="E88" s="13">
-        <v>9800</v>
+        <v>7510</v>
       </c>
       <c r="F88" s="13">
-        <v>11000</v>
+        <v>8850</v>
       </c>
       <c r="G88" s="16">
         <v>9</v>
       </c>
       <c r="H88" s="11"/>
     </row>
-    <row r="89" spans="1:8" ht="16.05" customHeight="1">
+    <row r="89" spans="1:8" ht="16" customHeight="1">
       <c r="A89" s="11" t="s">
         <v>37</v>
       </c>
@@ -3520,17 +3520,17 @@
         <v>220</v>
       </c>
       <c r="E89" s="13">
-        <v>7600</v>
+        <v>6350</v>
       </c>
       <c r="F89" s="13">
-        <v>8400</v>
+        <v>7900</v>
       </c>
       <c r="G89" s="16">
         <v>10</v>
       </c>
       <c r="H89" s="11"/>
     </row>
-    <row r="90" spans="1:8" ht="16.05" customHeight="1">
+    <row r="90" spans="1:8" ht="16" customHeight="1">
       <c r="A90" s="11" t="s">
         <v>37</v>
       </c>
@@ -3544,17 +3544,17 @@
         <v>222</v>
       </c>
       <c r="E90" s="13">
-        <v>3400</v>
+        <v>3650</v>
       </c>
       <c r="F90" s="13">
-        <v>4100</v>
+        <v>4350</v>
       </c>
       <c r="G90" s="16">
         <v>11</v>
       </c>
       <c r="H90" s="11"/>
     </row>
-    <row r="91" spans="1:8" ht="16.05" customHeight="1">
+    <row r="91" spans="1:8" ht="16" customHeight="1">
       <c r="A91" s="11" t="s">
         <v>37</v>
       </c>
@@ -3568,17 +3568,17 @@
         <v>224</v>
       </c>
       <c r="E91" s="13">
-        <v>4000</v>
+        <v>3300</v>
       </c>
       <c r="F91" s="13">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="G91" s="16">
         <v>12</v>
       </c>
       <c r="H91" s="11"/>
     </row>
-    <row r="92" spans="1:8" ht="16.05" customHeight="1">
+    <row r="92" spans="1:8" ht="16" customHeight="1">
       <c r="A92" s="11" t="s">
         <v>37</v>
       </c>
@@ -3592,17 +3592,17 @@
         <v>227</v>
       </c>
       <c r="E92" s="13">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="F92" s="13">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="G92" s="16">
         <v>1</v>
       </c>
       <c r="H92" s="11"/>
     </row>
-    <row r="93" spans="1:8" ht="16.05" customHeight="1">
+    <row r="93" spans="1:8" ht="16" customHeight="1">
       <c r="A93" s="11" t="s">
         <v>37</v>
       </c>
@@ -3616,17 +3616,17 @@
         <v>228</v>
       </c>
       <c r="E93" s="13">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="F93" s="13">
-        <v>3200</v>
+        <v>4200</v>
       </c>
       <c r="G93" s="16">
         <v>2</v>
       </c>
       <c r="H93" s="11"/>
     </row>
-    <row r="94" spans="1:8" ht="16.05" customHeight="1">
+    <row r="94" spans="1:8" ht="16" customHeight="1">
       <c r="A94" s="11" t="s">
         <v>37</v>
       </c>
@@ -3640,17 +3640,17 @@
         <v>230</v>
       </c>
       <c r="E94" s="13">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="F94" s="13">
-        <v>3550</v>
+        <v>4000</v>
       </c>
       <c r="G94" s="16">
         <v>3</v>
       </c>
       <c r="H94" s="11"/>
     </row>
-    <row r="95" spans="1:8" ht="16.05" customHeight="1">
+    <row r="95" spans="1:8" ht="16" customHeight="1">
       <c r="A95" s="11" t="s">
         <v>37</v>
       </c>
@@ -3664,17 +3664,17 @@
         <v>232</v>
       </c>
       <c r="E95" s="13">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="F95" s="13">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="G95" s="16">
         <v>4</v>
       </c>
       <c r="H95" s="11"/>
     </row>
-    <row r="96" spans="1:8" ht="16.05" customHeight="1">
+    <row r="96" spans="1:8" ht="16" customHeight="1">
       <c r="A96" s="11" t="s">
         <v>37</v>
       </c>
@@ -3688,17 +3688,17 @@
         <v>234</v>
       </c>
       <c r="E96" s="13">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="F96" s="13">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="G96" s="16">
         <v>5</v>
       </c>
       <c r="H96" s="11"/>
     </row>
-    <row r="97" spans="1:8" ht="16.05" customHeight="1">
+    <row r="97" spans="1:8" ht="16" customHeight="1">
       <c r="A97" s="11" t="s">
         <v>37</v>
       </c>
@@ -3712,17 +3712,17 @@
         <v>237</v>
       </c>
       <c r="E97" s="13">
-        <v>9450</v>
+        <v>8000</v>
       </c>
       <c r="F97" s="13">
-        <v>11850</v>
+        <v>13000</v>
       </c>
       <c r="G97" s="16">
         <v>1</v>
       </c>
       <c r="H97" s="11"/>
     </row>
-    <row r="98" spans="1:8" ht="16.05" customHeight="1">
+    <row r="98" spans="1:8" ht="16" customHeight="1">
       <c r="A98" s="11" t="s">
         <v>37</v>
       </c>
@@ -3736,17 +3736,17 @@
         <v>239</v>
       </c>
       <c r="E98" s="13">
-        <v>7775</v>
+        <v>8000</v>
       </c>
       <c r="F98" s="13">
-        <v>10750</v>
+        <v>13000</v>
       </c>
       <c r="G98" s="16">
         <v>2</v>
       </c>
       <c r="H98" s="11"/>
     </row>
-    <row r="99" spans="1:8" ht="16.05" customHeight="1">
+    <row r="99" spans="1:8" ht="16" customHeight="1">
       <c r="A99" s="11" t="s">
         <v>37</v>
       </c>
@@ -3760,17 +3760,17 @@
         <v>241</v>
       </c>
       <c r="E99" s="13">
-        <v>4775</v>
+        <v>5450</v>
       </c>
       <c r="F99" s="13">
-        <v>6850</v>
+        <v>7000</v>
       </c>
       <c r="G99" s="16">
         <v>3</v>
       </c>
       <c r="H99" s="11"/>
     </row>
-    <row r="100" spans="1:8" ht="16.05" customHeight="1">
+    <row r="100" spans="1:8" ht="16" customHeight="1">
       <c r="A100" s="11" t="s">
         <v>37</v>
       </c>
@@ -3784,17 +3784,17 @@
         <v>243</v>
       </c>
       <c r="E100" s="13">
-        <v>7000</v>
+        <v>7250</v>
       </c>
       <c r="F100" s="13">
-        <v>9500</v>
+        <v>8800</v>
       </c>
       <c r="G100" s="16">
         <v>4</v>
       </c>
       <c r="H100" s="11"/>
     </row>
-    <row r="101" spans="1:8" ht="16.05" customHeight="1">
+    <row r="101" spans="1:8" ht="16" customHeight="1">
       <c r="A101" s="11" t="s">
         <v>37</v>
       </c>
@@ -3808,17 +3808,17 @@
         <v>245</v>
       </c>
       <c r="E101" s="13">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="F101" s="13">
-        <v>6150</v>
+        <v>7000</v>
       </c>
       <c r="G101" s="16">
         <v>5</v>
       </c>
       <c r="H101" s="11"/>
     </row>
-    <row r="102" spans="1:8" ht="16.05" customHeight="1">
+    <row r="102" spans="1:8" ht="16" customHeight="1">
       <c r="A102" s="11" t="s">
         <v>37</v>
       </c>
@@ -3835,14 +3835,14 @@
         <v>4400</v>
       </c>
       <c r="F102" s="13">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="G102" s="16">
         <v>1</v>
       </c>
       <c r="H102" s="11"/>
     </row>
-    <row r="103" spans="1:8" ht="16.05" customHeight="1">
+    <row r="103" spans="1:8" ht="16" customHeight="1">
       <c r="A103" s="11" t="s">
         <v>37</v>
       </c>
@@ -3856,17 +3856,17 @@
         <v>250</v>
       </c>
       <c r="E103" s="13">
-        <v>4250</v>
+        <v>4300</v>
       </c>
       <c r="F103" s="13">
-        <v>6600</v>
+        <v>6950</v>
       </c>
       <c r="G103" s="16">
         <v>2</v>
       </c>
       <c r="H103" s="11"/>
     </row>
-    <row r="104" spans="1:8" ht="16.05" customHeight="1">
+    <row r="104" spans="1:8" ht="16" customHeight="1">
       <c r="A104" s="11" t="s">
         <v>37</v>
       </c>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="H104" s="11"/>
     </row>
-    <row r="105" spans="1:8" ht="16.05" customHeight="1">
+    <row r="105" spans="1:8" ht="16" customHeight="1">
       <c r="A105" s="11" t="s">
         <v>37</v>
       </c>
@@ -3904,17 +3904,17 @@
         <v>254</v>
       </c>
       <c r="E105" s="13">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="F105" s="13">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G105" s="16">
         <v>4</v>
       </c>
       <c r="H105" s="11"/>
     </row>
-    <row r="106" spans="1:8" ht="16.05" customHeight="1">
+    <row r="106" spans="1:8" ht="16" customHeight="1">
       <c r="A106" s="11" t="s">
         <v>37</v>
       </c>
@@ -3928,17 +3928,17 @@
         <v>256</v>
       </c>
       <c r="E106" s="13">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="F106" s="13">
-        <v>6500</v>
+        <v>6550</v>
       </c>
       <c r="G106" s="16">
         <v>5</v>
       </c>
       <c r="H106" s="11"/>
     </row>
-    <row r="107" spans="1:8" ht="16.05" customHeight="1">
+    <row r="107" spans="1:8" ht="16" customHeight="1">
       <c r="A107" s="12" t="s">
         <v>37</v>
       </c>
